--- a/Backup/eGP_Monthly_Main_202606.xlsx
+++ b/Backup/eGP_Monthly_Main_202606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,8 @@
           <t>สำนักงานคณะกรรมการข้าราชการพลเรือน</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0111</t>
-        </is>
+      <c r="C2" t="n">
+        <v>111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -513,10 +511,8 @@
           <t>สำนักงานกองทุนสนับสนุนการสร้างเสริมสุขภาพ</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0117</t>
-        </is>
+      <c r="C3" t="n">
+        <v>117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -550,10 +546,8 @@
           <t>สำนักงานเศรษฐกิจการเกษตร</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0715</t>
-        </is>
+      <c r="C4" t="n">
+        <v>715</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -587,10 +581,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C5" t="n">
+        <v>804</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -624,10 +616,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -661,10 +651,8 @@
           <t>กรมสนับสนุนบริการสุขภาพ</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
+      <c r="C7" t="n">
+        <v>2107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -684,6 +672,265 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=822137b2-4a8c-48a5-92e3-9014fbb7d4b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>สำนักงานส่งเสริมเศรษฐกิจสร้างสรรค์ (องค์การมหาชน)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0137</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=add95820-1482-47aa-8da6-6f94caea2766</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างจ้างปรับปรุงพื้นที่ศูนย์ไฮโดรเจนสมดุลเพื่อความยั่งยืน ระบบครุภัณฑ์สำหรับพัฒนาไฮโดรเจนสมดุลเพื่อความยั่งยืน ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 ระบบ (ครั้งที่ 2) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=dde4fbc7-7ad2-42f3-ab54-523b82ae315c</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 4 รายการ สำหรับโรงพยาบาลชุมชนในสังกัด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1216bc39-fa7a-4245-8d5b-7866e6421779</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว จำนวน 15 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>★ (ตู้เย็น)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d62001fd-1719-40b4-a897-6144ec751ac9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาสตร์ จำนวน ๔ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7048f7ad-49b8-471e-96ee-e3578cbd0104</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>กรมวิทยาศาสตร์การแพทย์</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างบำรุงรักษาระบบสารสนเทศงานตรวจคัดกรองสุขภาพทารกแรกเกิด Newborn Connect และบำรุงรักษาเครื่องคอมพิวเตอร์แม่ข่ายและอุปกรณ์เครือข่ายที่เกี่ยวข้อง จำนวน ๑ งาน ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3c90c995-62a3-43c6-b4c2-7be1d7b388c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>สถาบันพระบรมราชชนก</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์โสตทัศนูปกรณ์ห้องเรียนอัจฉริยะ Smart Classroom ประจำปีงบประมาณ 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5d903eb8-899a-43d3-aeb4-0b9be5b56c37</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202606.xlsx
+++ b/Backup/eGP_Monthly_Main_202606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,10 +686,8 @@
           <t>สำนักงานส่งเสริมเศรษฐกิจสร้างสรรค์ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0137</t>
-        </is>
+      <c r="C8" t="n">
+        <v>137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -723,10 +721,8 @@
           <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -760,10 +756,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C10" t="n">
+        <v>2102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -797,10 +791,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -834,10 +826,8 @@
           <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="C12" t="n">
+        <v>2106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -871,10 +861,8 @@
           <t>กรมวิทยาศาสตร์การแพทย์</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="C13" t="n">
+        <v>2106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -908,10 +896,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C14" t="n">
+        <v>2117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -931,6 +917,302 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5d903eb8-899a-43d3-aeb4-0b9be5b56c37</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>สำนักงบประมาณ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อหน่วยความจำหลัก (RAM) ประเภท DDR4 ขนาด 8 GB 559 หน่วย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>★ (หน่วยความจำ)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=27681699-def2-4d3b-b594-b1c2488d8416</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อหมึกพิมพ์สนับสนุนงานสารสนเทศ ศรภ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>★ (หมึกพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4f623f39-fdba-4c92-9f87-4d8de9cf238d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจัดหาพร้อมติดตั้งระบบควบคุมมอเตอร์ไฟฟ้าสำหรับเครื่องสูบน้ำให้ใช้งานได้ (ระบบส่งน้ำสถานีสูบน้ำด้วยไฟฟ้าดอนแสลบ 1 ตำบลดอนแสลบ อำเภอห้วยกระเจา จังหวัดกาญจนบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5b027ffc-9be3-4d25-9ad8-c97cddce3c7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเกษตร</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0711</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อลิขสิทธิ์และการรับประกันอุปกรณ์ระบบควบคุมทราฟฟิกเครือข่ายคอมพิวเตอร์ (ML-Firewall) จำนวน 1 ระบบ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c7eaff93-a86d-40c3-8553-f5d0e5c068d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>กรมป้องกันและบรรเทาสาธารณภัย</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อลิขสิทธิ์การใช้งานซอฟต์แวร์ไมโครซอฟท์ระดับองค์กร ประจำปีงบประมาณ พ.ศ. 2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c70dc5a1-ff5e-4a6a-93ab-2a31cc27eb16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>กรมคุ้มครองสิทธิและเสรีภาพ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1604</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อวัสดุคอมพิวเตอร์ ประจำปีงบประมาณ ๒๕๖๙ (รอบ ๖ เดือนหลัง) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3e136cfd-f37e-4ca6-8db6-7ef901969dde</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>กรมการจัดหางาน</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์คอมพิวเตอร์ทดแทนและเพิ่มประสิทธิภาพของสำนักบริหารแรงงานต่างด้าว ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08d02122-7eb2-45aa-b5be-4b4e318eb4d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>กรมควบคุมโรค</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน 12 รายการ โดยวิธีประกาศเชิญชวนทั่วไป ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=53f40c00-b5c3-406d-8125-72df4b4d483f</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202606.xlsx
+++ b/Backup/eGP_Monthly_Main_202606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,10 +931,8 @@
           <t>สำนักงบประมาณ</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0107</t>
-        </is>
+      <c r="C15" t="n">
+        <v>107</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -968,10 +966,8 @@
           <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0208</t>
-        </is>
+      <c r="C16" t="n">
+        <v>208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1005,10 +1001,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C17" t="n">
+        <v>703</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1042,10 +1036,8 @@
           <t>กรมส่งเสริมการเกษตร</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0711</t>
-        </is>
+      <c r="C18" t="n">
+        <v>711</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1079,10 +1071,8 @@
           <t>กรมป้องกันและบรรเทาสาธารณภัย</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1506</t>
-        </is>
+      <c r="C19" t="n">
+        <v>1506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1116,10 +1106,8 @@
           <t>กรมคุ้มครองสิทธิและเสรีภาพ</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
+      <c r="C20" t="n">
+        <v>1604</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1153,10 +1141,8 @@
           <t>กรมการจัดหางาน</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="C21" t="n">
+        <v>1703</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1190,10 +1176,8 @@
           <t>กรมควบคุมโรค</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
+      <c r="C22" t="n">
+        <v>2104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1213,6 +1197,265 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=53f40c00-b5c3-406d-8125-72df4b4d483f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>สำนักงานเศรษฐกิจการคลัง</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0311</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าโครงการค่าเช่ารถนั่งส่วนกลาง รถยนต์ไฟฟ้า ประเภทแบตเตอรี่ (BEV) (ขนาดความจุของแบตเตอรี่ตั้งแต่ 30 กิโลวัตต์ชั่วโมง (kWh) ขึ้นไป และกำลังมอเตอร์ไฟฟ้าสูงสุดไม่เกิน 150 กิโลวัตต์) 4 คัน ระยะเวลา 5 ปี (60 เดือน) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d2faa91f-8db3-4c69-b0de-2cc26eeb0dbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>กรมการข้าว</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0718</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ประจำคลังเมล็ดพันธุ์ แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร จำนวน ๖ ชุด ครั้งที่ ๓ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e58546a7-6bca-467c-b666-7ea59af53783</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างระบบครุภัณฑ์สำหรับการผลิตไบโอชาร์ ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี  ต้นแบบเตาผลิตไบโอชาร์แบบต่อเนื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f4e52ac7-8ea1-4631-8418-c93def61c1ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>สำนักงานสภานโยบายการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรมแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าคอมพิวเตอร์พร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f9f01104-11f8-4f6b-b9e3-5db69e0a0987</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์เทคโนโลยีดิจิทัลเพื่อการเรียนรู้ตลอดชีวิต ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ca4757ab-1a5e-473e-82b2-998170bdd909</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องเอกซเรย์เคลื่อนที่ขนาดไม่น้อยกว่า ๓๐๐ mA ขับเคลื่อนด้วยมอเตอร์ไฟฟ้า จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=eba6eb50-895e-4ebc-a83c-88dcf1227dd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa83154-da8b-4f72-8f90-ff5b56480cbc</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202606.xlsx
+++ b/Backup/eGP_Monthly_Main_202606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,10 +1211,8 @@
           <t>สำนักงานเศรษฐกิจการคลัง</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0311</t>
-        </is>
+      <c r="C23" t="n">
+        <v>311</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1248,10 +1246,8 @@
           <t>กรมการข้าว</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0718</t>
-        </is>
+      <c r="C24" t="n">
+        <v>718</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1285,10 +1281,8 @@
           <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
+      <c r="C25" t="n">
+        <v>1905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1322,10 +1316,8 @@
           <t>สำนักงานสภานโยบายการอุดมศึกษา วิทยาศาสตร์ วิจัยและนวัตกรรมแห่งชาติ</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1359,10 +1351,8 @@
           <t>กรมส่งเสริมการเรียนรู้</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="C27" t="n">
+        <v>2033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1396,10 +1386,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C28" t="n">
+        <v>2102</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1433,29 +1421,249 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa83154-da8b-4f72-8f90-ff5b56480cbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการกฤษฎีกา</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0109</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการต่ออายุการให้การสนับสนุนผลิตภัณฑ์และลิขสิทธิ์ซอฟต์แวร์สำหรับอุปกรณ์เครือข่าย ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>★ (อุปกรณ์เครือข่าย, ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=09f27807-dd9d-4fab-bbb1-5fda4eff1f7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>กองอำนวยการรักษาความมั่นคงภายใน</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0119</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องคอมพิวเตอร์สำหรับงานประมวลผลและอุปกรณ์ ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ สนับสนุน นขต.กอ.รมน.   ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=b515d88b-9bb5-4190-9c73-4b239086b996</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริหารโครงการปรับปรุง-ซ่อมแซม เสาส่งสัญญาณโทรทัศน์ จำนวน 3 ต้น  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>★ (โทรทัศน์)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a43df71b-a540-4a40-a10b-4ee8ceb5b87e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโปรแกรมป้องกันไวรัสคอมพิวเตอร์ (Antivirus) จำนวน ๑๐,๐๐๐ ใบอนุญาต (Licenses) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โปรแกรมป้องกันไวรัส)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5fcba089-ca9c-44fc-8f48-ac63abac665d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องให้การรักษาทางกายภาพด้วยคลื่นแม่เหล็กไฟฟ้า จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน 9 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=faa83154-da8b-4f72-8f90-ff5b56480cbc</t>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=16a8ba02-2ba9-44ed-8ecc-444f18f1daab</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>กรมควบคุมโรค</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3e3e632a-b72f-481a-830c-5af4fa6c476d</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202606.xlsx
+++ b/Backup/eGP_Monthly_Main_202606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,10 +1456,8 @@
           <t>สำนักงานคณะกรรมการกฤษฎีกา</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0109</t>
-        </is>
+      <c r="C30" t="n">
+        <v>109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1493,10 +1491,8 @@
           <t>กองอำนวยการรักษาความมั่นคงภายใน</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0119</t>
-        </is>
+      <c r="C31" t="n">
+        <v>119</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1530,10 +1526,8 @@
           <t>องค์การกระจายเสียงและแพร่ภาพสาธารณะแห่งประเทศไทย(ส.ส.ท.)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0915</t>
-        </is>
+      <c r="C32" t="n">
+        <v>915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1567,10 +1561,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C33" t="n">
+        <v>1505</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1604,10 +1596,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C34" t="n">
+        <v>2102</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1641,10 +1631,8 @@
           <t>กรมควบคุมโรค</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
+      <c r="C35" t="n">
+        <v>2104</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1664,6 +1652,265 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3e3e632a-b72f-481a-830c-5af4fa6c476d</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>กองบัญชาการกองทัพไทย</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างทำขวดบรรจุน้ำดื่ม ขนาด ๓๕๐ ซีซี พร้อมตราสัญลักษณ์ บก.ทท. ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ (ครั้งที่ ๒) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>★ (น้ำดื่ม)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c108754c-bf65-45f0-b7fc-8eb19266e519</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครือข่ายคอมพิวเตอร์และระบบต่าง ๆ ที่เกี่ยวข้องที่อาคารศรีอยุธยา อาคารกรมการกงสุล และอาคารศูนย์ราชการเฉลิมพระเกียรติฯ จำนวน ๑๒ เดือน ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1a8009a1-188f-4759-8bf6-33f8320c1516</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดหาชุดไมโครโฟนห้องประชุมพร้อมติดตั้ง แขวงลาดยาว เขตจตุจักร กรุงเทพมหานคร 1 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>★ (ไมโครโฟน)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d41830a2-6267-4094-b00c-d87852d9fb5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>กรมประมง</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0705</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์โน้ตบุ๊ก เพื่อเพิ่มประสิทธิภาพการปฏิบัติงานของประมงอำเภอ จำนวน 15 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, โน้ตบุ๊ก, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=46622699-a897-434b-bd30-66be46756f09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>กรมปศุสัตว์</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0706</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างซ่อมชุดทำความเข้มข้น Ultrafiltration ชนิด Cassette รหัสครุภัณฑ์ ๐๖๑๒-๑๑-๒๖-๐๒๓-๐๐๐๑ ๕๘ จำนวน ๑ ชุด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=495ffff7-6a6e-4511-b239-f9cb4f217d01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>กรมราชทัณฑ์</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1607</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์เพื่อพัฒนาคุณภาพชีวิตด้านสุขภาพจิต โดยใช้ดนตรีบำบัด สำหรับผู้ต้องขังเรือนจำกลางระยอง ตำบลหนองละลอก อำเภอบ้านค่าย จังหวัดระยอง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f415d0d4-b637-4b10-9b4d-dc6ee4192f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการอาหารและยา</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างต่ออายุลิขสิทธิ์ซอฟต์แวร์สำหรับระบบเชื่อมโยง NSW ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8344d9f-1d1a-4e01-a893-9216a24255b2</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202606.xlsx
+++ b/Backup/eGP_Monthly_Main_202606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>กองบัญชาการกองทัพไทย</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0208</t>
-        </is>
+      <c r="C36" t="n">
+        <v>208</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1703,10 +1701,8 @@
           <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
+      <c r="C37" t="n">
+        <v>402</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1740,10 +1736,8 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C38" t="n">
+        <v>705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1777,10 +1771,8 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C39" t="n">
+        <v>705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1814,10 +1806,8 @@
           <t>กรมปศุสัตว์</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0706</t>
-        </is>
+      <c r="C40" t="n">
+        <v>706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1851,10 +1841,8 @@
           <t>กรมราชทัณฑ์</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1607</t>
-        </is>
+      <c r="C41" t="n">
+        <v>1607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1888,10 +1876,8 @@
           <t>สำนักงานคณะกรรมการอาหารและยา</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2110</t>
-        </is>
+      <c r="C42" t="n">
+        <v>2110</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1911,6 +1897,413 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a8344d9f-1d1a-4e01-a893-9216a24255b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>สำนักงบประมาณ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อหมึกพิมพ์ จำนวน 25 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>★ (หมึกพิมพ์)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=026f0e50-d0ef-4209-9382-d021859d6511</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานเปลี่ยนเครื่องปรับอากาศทดแทน อาคารเรียนและปฏิบัติการชั้น ๒ - ๔ ของ วิทยาลัยพยาบาลกองทัพบก กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7ec2d4c3-e977-4b4f-b3d5-4d8b56d7d26b</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>กองทัพอากาศ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0206</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเก้าอี้ทำงาน ระดับฝ่าย จำนวน ๑๑๕ ตัว (แจ้งที่ ๘๐๗/๖๙) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>★ (เก้าอี้)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7116d885-8622-4d83-9678-1eed9f2f5a79</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ อุปกรณ์การประมวลผลและระบบคอมพิวเตอร์ โครงการพัฒนาระบบการยืนยันตัวบุคคล ประจำปีงบประมาณ พ.ศ. ๒๕๖๙ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=91eb3911-20bf-48b9-b2b9-08efec177417</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างพิมพ์กระดาษ สติ๊กเกอร์แผ่นปะและส่วนประกอบอื่น ๆ ที่มีคุณสมบัติป้องกันการปลอมแปลงพิเศษสำหรับนิติกรณ์เอกสาร Apostille ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>★ (กระดาษ)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f9f1e8f5-85a5-46d7-b31f-600f1a914a1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาสังคมและสวัสดิการ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดหาครุภัณฑ์คอมพิวเตอร์พร้อมอุปกรณ์ เพื่อสนับสนุนการปฏิบัติงานนิคมสร้างตนเอง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=fca8135d-06ca-4b7a-b9bd-cb6b5c48d8f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมและพัฒนาคุณภาพชีวิตคนพิการ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0607</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์สำนักงาน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=88519162-5263-42c3-8dc9-19276cc7759c</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อคอมพิวเตอร์แท็บเล็ต เพื่อพัฒนาประสิทธิภาพงานตรวจสอบทรัพย์สินคดียาเสพติด และการบริหารงานกองทุนป้องกัน ปราบปราม และแก้ไขปัญหายาเสพติด ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, แท็บเล็ต)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f6c74fae-1bc5-4e9c-8a9a-d767f5c0edab</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อพร้อมติดตั้งเครื่องปรับอากาศอาคารศูนย์ประชุมอุทยานวิทยาศาสตร์ประเทศไทย ค่าปรับปรุง ซ่อมแซมอาคารสถานที่ในพื้นที่อุทยานวิทยาศาสตร์ประเทศไทย ตำบลคลองหนึ่ง อำเภอคลองหลวง จังหวัดปทุมธานี 1 แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=084dd3c5-6b02-4544-9ed2-cc0919e8bcff</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการยูนิตทำฟัน โรงพยาบาลส่งเสริมสุขภาพตำบลและโรงพยาบาลชุมชน จังหวัดสุรินทร์ จำนวน 4  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=88608380-c2d4-47b9-9e12-7e9786aed808</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์วิทยาศาตร์การแพทย์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bdde6ad9-e46e-4f8c-abb7-a76e9127502a</t>
         </is>
       </c>
     </row>
